--- a/schemas/template/schema-crate/ro-crate-metadata.xlsx
+++ b/schemas/template/schema-crate/ro-crate-metadata.xlsx
@@ -238,12 +238,18 @@
     <t>Role indicating a resource is an editor configuration mode file.</t>
   </si>
   <si>
+    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/1149</t>
+  </si>
+  <si>
+    <t>DigitalFormat</t>
+  </si>
+  <si>
+    <t>Markdown</t>
+  </si>
+  <si>
     <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/817</t>
   </si>
   <si>
-    <t>DigitalFormat</t>
-  </si>
-  <si>
     <t>JSON Data Interchange Format</t>
   </si>
   <si>
@@ -251,12 +257,6 @@
   </si>
   <si>
     <t>Hypertext Markup Language</t>
-  </si>
-  <si>
-    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/1149</t>
-  </si>
-  <si>
-    <t>Markdown</t>
   </si>
 </sst>
 </file>
